--- a/ACCOUNT_RECEIPT/tests/DatasheetKDMC Updated.xlsx
+++ b/ACCOUNT_RECEIPT/tests/DatasheetKDMC Updated.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,6 +452,9 @@
       <c r="P1" t="str">
         <v>Receipt No</v>
       </c>
+      <c r="Q1" t="str">
+        <v>Status</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -494,7 +497,10 @@
         <v>21300</v>
       </c>
       <c r="P2" t="str">
-        <v>AC40565</v>
+        <v>AC40572</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Done</v>
       </c>
     </row>
     <row r="3">
@@ -538,10 +544,13 @@
         <v>21300</v>
       </c>
       <c r="P3" t="str">
-        <v>AC40566</v>
+        <v>AC40573</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Done</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>20022026</v>
       </c>
@@ -581,13 +590,16 @@
       <c r="O4" t="str">
         <v>21300</v>
       </c>
-      <c r="P4" t="str">
-        <v>AC40567</v>
+      <c r="Q4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: locator.fill: Target page, context or browser has been closed
+Call log:
+_x001b_[2m  - waiting for locator('#transactionDateId')_x001b_[22m
+</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
   </ignoredErrors>
 </worksheet>
 </file>